--- a/backend/raw_data/listados.xlsx
+++ b/backend/raw_data/listados.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luis.aguilar\Documents\GitHub\inteligencia_estrategica_precios\backend\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A727E3C1-F597-4C23-8A02-A5626AD7FA83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560BA501-30F7-4E69-9541-7C2545636C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E5C1C4F-9DFD-4C7A-AD36-4DAE56DD4344}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="test" sheetId="2" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$G$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja1!$A$1:$G$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">test!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="71">
   <si>
     <t>competencia</t>
   </si>
@@ -59,9 +61,6 @@
     <t>url_listado</t>
   </si>
   <si>
-    <t>vigente</t>
-  </si>
-  <si>
     <t>Liverpool</t>
   </si>
   <si>
@@ -252,14 +251,25 @@
   </si>
   <si>
     <t>Belleza, Infantil</t>
+  </si>
+  <si>
+    <t>activo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -287,8 +297,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -622,6 +633,148 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EB1463E-16D9-49D3-A586-DBA727C2D861}">
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="166.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="18" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="19" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="20" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="21" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="22" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="23" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="24" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="25" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="26" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="27" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="28" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="29" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="30" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="31" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="32" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="33" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="34" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <autoFilter ref="A1:G4" xr:uid="{D3F513AE-976D-48B1-ACBC-D2412360CF7F}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3F513AE-976D-48B1-ACBC-D2412360CF7F}">
   <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -655,881 +808,881 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
         <v>8</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>9</v>
       </c>
-      <c r="E9" t="s">
-        <v>21</v>
-      </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>9</v>
       </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
         <v>8</v>
       </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
         <v>8</v>
       </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
         <v>8</v>
       </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
         <v>8</v>
       </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
         <v>8</v>
       </c>
-      <c r="D15" t="s">
-        <v>25</v>
-      </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
         <v>8</v>
       </c>
-      <c r="D16" t="s">
-        <v>25</v>
-      </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
         <v>8</v>
       </c>
-      <c r="D17" t="s">
-        <v>34</v>
-      </c>
       <c r="E17" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F18" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="F21" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="F22" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="G23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="F24" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E25" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="F25" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E26" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="F26" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E27" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="F27" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" t="s">
         <v>40</v>
       </c>
-      <c r="D28" t="s">
-        <v>46</v>
-      </c>
       <c r="E28" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F28" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" t="s">
         <v>40</v>
       </c>
-      <c r="D29" t="s">
-        <v>46</v>
-      </c>
       <c r="E29" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F29" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="G29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D30" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E30" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="F30" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E31" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F31" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E32" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F32" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="G32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E33" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F33" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="G33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C34" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D34" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E34" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F34" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="G34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F35" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D36" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E36" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F36" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C37" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D37" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E37" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F37" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C38" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D38" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E38" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F38" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D39" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E39" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F39" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
